--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,337 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129703075</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nördstberg, Nördstberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>449503</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6783372</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129703495</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nördstberg, Nördstberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>449536</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6783406</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129703576</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56925</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nördstberg, Nördstberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>449540</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6783407</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129703075</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129703495</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129703576</v>
       </c>
       <c r="B5" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129703495</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129703075</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129703495</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129703576</v>
       </c>
       <c r="B5" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129703075</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129703495</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129703576</v>
       </c>
       <c r="B5" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129703495</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51896-2025 artfynd.xlsx
+++ b/artfynd/A 51896-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129703495</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
